--- a/data/taxo.xlsx
+++ b/data/taxo.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\pop-these\resultat\dbcan_results\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\eDNA Collaborative 2\Downloads\moi\revision_ACMI\Final analysis\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{ACC2DBF9-528E-4487-9245-A4F74E9D40DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AF0A3F1-8C98-4CAA-B5AB-1358BF1FEB88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{95F77CC3-8774-4C25-8673-6A386098826A}"/>
   </bookViews>
@@ -331,30 +331,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -369,11 +351,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -392,9 +372,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office 2013 – 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -432,7 +412,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -538,7 +518,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -680,7 +660,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -691,18 +671,19 @@
   <dimension ref="A1:C50"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="139.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="139.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.5546875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
@@ -740,10 +721,10 @@
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="A5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C5" s="1">
@@ -751,21 +732,21 @@
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+      <c r="A6" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="1">
         <v>11.27913</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+      <c r="A7" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="1" t="s">
         <v>14</v>
       </c>
       <c r="C7" s="1">
@@ -773,418 +754,418 @@
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C8" s="2">
+      <c r="C8" s="1">
         <v>0.48508000000000001</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
+      <c r="A9" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="1">
         <v>2.7999999999999998E-4</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
+      <c r="A10" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C10">
+      <c r="C10" s="1">
         <v>23.322189999999999</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
+      <c r="A11" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C11">
+      <c r="C11" s="1">
         <v>0.73353999999999997</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
+      <c r="A12" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C12">
+      <c r="C12" s="1">
         <v>2.3792800000000001</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
+      <c r="A13" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C13">
+      <c r="C13" s="1">
         <v>4.5353000000000003</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A14" s="2" t="s">
+      <c r="A14" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C14" s="2">
+      <c r="C14" s="1">
         <v>5.3219599999999998</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
+      <c r="A15" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C15">
+      <c r="C15" s="1">
         <v>3.4191790000000002</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
+      <c r="A16" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C16">
+      <c r="C16" s="1">
         <v>7.4025600000000003</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
+      <c r="A17" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C17">
+      <c r="C17" s="1">
         <v>0.50888</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
+      <c r="A18" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B18" s="1" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
+      <c r="A19" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C19">
+      <c r="C19" s="1">
         <v>0.37475999999999998</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
+      <c r="A20" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C20">
+      <c r="C20" s="1">
         <v>0.51473999999999998</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
+      <c r="A21" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="B21" s="1" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
+      <c r="A22" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="B22" s="1" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
+      <c r="A23" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="B23" s="1" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
+      <c r="A24" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="B24" s="1" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
+      <c r="A25" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="B25" s="1" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
+      <c r="A26" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B26" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C26">
+      <c r="C26" s="1">
         <v>0.13270000000000001</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
+      <c r="A27" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B27" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="C27">
+      <c r="C27" s="1">
         <v>11.628080000000001</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
+      <c r="A28" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B28" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="C28">
+      <c r="C28" s="1">
         <v>0.88071999999999995</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
+      <c r="A29" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B29" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="C29">
+      <c r="C29" s="1">
         <v>1.3447899999999999</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
+      <c r="A30" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="B30" s="3" t="s">
+      <c r="B30" s="1" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
+      <c r="A31" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B31" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="C31">
+      <c r="C31" s="1">
         <v>8.9200000000000008E-3</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
+      <c r="A32" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="B32" s="3" t="s">
+      <c r="B32" s="1" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
+      <c r="A33" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="B33" s="3" t="s">
+      <c r="B33" s="1" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
+      <c r="A34" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="B34" s="3" t="s">
+      <c r="B34" s="1" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
+      <c r="A35" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="B35" s="3" t="s">
+      <c r="B35" s="1" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
+      <c r="A36" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="B36" s="3" t="s">
+      <c r="B36" s="1" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
+      <c r="A37" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="B37" s="3" t="s">
+      <c r="B37" s="1" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
+      <c r="A38" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B38" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="C38">
+      <c r="C38" s="1">
         <v>1.1705999999999999</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
+      <c r="A39" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B39" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="C39">
+      <c r="C39" s="1">
         <v>0.79824000000000006</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A40" t="s">
+      <c r="A40" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B40" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="C40">
+      <c r="C40" s="1">
         <v>1.1705999999999999</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
+      <c r="A41" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="B41" s="3" t="s">
+      <c r="B41" s="1" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
+      <c r="A42" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="B42" t="s">
+      <c r="B42" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="C42">
+      <c r="C42" s="1">
         <v>3.8601800000000006</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A43" t="s">
+      <c r="A43" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="B43" t="s">
+      <c r="B43" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="C43">
+      <c r="C43" s="1">
         <v>0.30358000000000002</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A44" t="s">
+      <c r="A44" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="B44" t="s">
+      <c r="B44" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="C44">
+      <c r="C44" s="1">
         <v>0.79824000000000006</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A45" t="s">
+      <c r="A45" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="B45" s="3" t="s">
+      <c r="B45" s="1" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A46" t="s">
+      <c r="A46" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="B46" s="3" t="s">
+      <c r="B46" s="1" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A47" t="s">
+      <c r="A47" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="B47" s="3" t="s">
+      <c r="B47" s="1" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A48" t="s">
+      <c r="A48" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="B48" s="3" t="s">
+      <c r="B48" s="1" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A49" t="s">
+      <c r="A49" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="B49" s="3" t="s">
+      <c r="B49" s="1" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A50" t="s">
+      <c r="A50" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="B50" t="s">
+      <c r="B50" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="C50">
+      <c r="C50" s="1">
         <v>1.6263400000000001</v>
       </c>
     </row>
